--- a/public/templates/forms/A-035-AccessEntitlementMatrix-FORM.xlsx
+++ b/public/templates/forms/A-035-AccessEntitlementMatrix-FORM.xlsx
@@ -1,59 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Matrix" sheetId="1" r:id="rId1"/>
-    <sheet name="Column Instructions" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="11">
+    <font>
+      <name val="Aptos"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF1B3A5C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3A5C"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F7"/>
+        <bgColor rgb="FFF4F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F1E8"/>
+        <bgColor rgb="FFEEF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3A5C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -61,18 +124,202 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF4F1E8"/>
+      <rgbColor rgb="FFEEF2F7"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF1B3A5C"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -119,12 +366,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -254,255 +501,344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="22"/>
-    <col min="2" max="2" customWidth="1" width="26"/>
-    <col min="3" max="3" customWidth="1" width="18"/>
-    <col min="4" max="4" customWidth="1" width="30"/>
-    <col min="5" max="5" customWidth="1" width="16"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" t="str">
-        <v>Access Entitlement Matrix</v>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Access Entitlement Matrix</t>
+        </is>
       </c>
     </row>
     <row r="2" ht="29.75" customHeight="1">
-      <c r="A2"/>
+      <c r="A2" s="8" t="n"/>
     </row>
     <row r="3" ht="29.75" customHeight="1">
-      <c r="A3" t="str">
-        <v>Authority</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3" t="str">
-        <v>Adopted by {agencyName} under the authority of {signingOfficialTitle}.</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3"/>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Adopted by [Agency Name] under the authority of [signing official / title].</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="17" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4" t="str">
-        <v>[Role title]   « use a role, not a person’s name »</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4"/>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>[Role title]   « use a role, not a person’s name »</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="17" t="n"/>
     </row>
     <row r="5" ht="29.75" customHeight="1">
-      <c r="A5" t="str">
-        <v>Version / Dates</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5" t="str">
-        <v>Version {version}      Effective Date {effectiveDate}      Next Review {effectiveDate}</v>
-      </c>
-      <c r="D5"/>
-      <c r="E5"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Version / Dates</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Version [#]      Effective Date [Date]      Next Review [Date]</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="17" t="n"/>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="A6" t="str">
-        <v>Classification</v>
-      </c>
-      <c r="B6"/>
-      <c r="C6" t="str">
-        <v>Restricted / CJIS   « Minimum for this matrix: it reveals operational access architecture and covers CJIS-regulated systems via IDACS. Your agency may raise but not lower. »</v>
-      </c>
-      <c r="D6"/>
-      <c r="E6"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Restricted / CJIS   « Minimum for this matrix: it reveals operational access architecture and covers CJIS-regulated systems via IDACS. Your agency may raise but not lower. »</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="17" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="str">
-        <v>Purpose and Scope</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Purpose and Scope</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" t="str">
-        <v>Defines the authorized access baseline: which systems and data each staff role and vendor type may reach, and at what access level. It is the least-privilege reference that access reviews check against.</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Defines the authorized access baseline: which systems and data each staff role and vendor type may reach, and at what access level. It is the least-privilege reference that access reviews check against.</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="str">
-        <v>How to Read This Matrix</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>How to Read This Matrix</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="str">
-        <v>« Explain the row dimension, the column dimension, and what a cell value means. »</v>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>« Explain the row dimension, the column dimension, and what a cell value means. »</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" t="str">
-        <v>Each row is one authorized grant: a role or vendor type paired with a system or data set and the access level allowed. The matrix is role-indexed; it states what each role may access, not who holds the role. The person-to-role assignment lives in the Account-to-Role Assignment Register, and reconciliation against live accounts is evidenced in the Privilege Review Records and Periodic Account Review / Certification Records.</v>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Each row is one authorized grant: a role or vendor type paired with a system or data set and the access level allowed. The matrix is role-indexed; it states what each role may access, not who holds the role. The person-to-role assignment lives in the Account-to-Role Assignment Register, and reconciliation against live accounts is evidenced in the Privilege Review Records and Periodic Account Review / Certification Records.</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="str">
-        <v>Matrix</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="str">
-        <v>« Replace the corner, column headers, and row labels with the dimensions this matrix maps (e.g., role × system, control × artifact). Add rows and columns as needed. »</v>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>« Replace the corner, column headers, and row labels with the dimensions this matrix maps (e.g., role × system, control × artifact). Add rows and columns as needed. »</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
-      <c r="A17" t="str">
-        <v>Role / Vendor type</v>
-      </c>
-      <c r="B17" t="str">
-        <v>System or data set</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Access level (read / write / admin)</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Conditions / authorizing basis</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Last reviewed</v>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Role / Vendor type</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>System or data set</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Access level (read / write / admin)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Conditions / authorizing basis</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Last reviewed</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="str">
-        <v>Notes and Exceptions</v>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Notes and Exceptions</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="str">
-        <v>« Anything the grid cannot capture: caveats, exceptions, effective dates. »</v>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>« Anything the grid cannot capture: caveats, exceptions, effective dates. »</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" t="str">
-        <v>[Record time-boxed elevations, break-glass access, and role exceptions, each with expiry and approving authority. Mirror persistent exceptions into the Risk / Finding Register (POA&amp;M).]</v>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>[Record time-boxed elevations, break-glass access, and role exceptions, each with expiry and approving authority. Mirror persistent exceptions into the Risk / Finding Register (POA&amp;M).]</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="str">
-        <v>Review Schedule and Ownership</v>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Review Schedule and Ownership</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="str">
-        <v>Reviewed at least [quarterly] by the [role], and reconciled against active accounts each cycle. Update on any role or system change.</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Reviewed at least [quarterly] by the [role], and reconciled against active accounts each cycle. Update on any role or system change.</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="str">
-        <v>Source Authority</v>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Source Authority</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="29.75" customHeight="1">
-      <c r="A33" t="str">
-        <v>« List only the authorities that map to this artifact. Group by authority; order numerically. No padding. »</v>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>« List only the authorities that map to this artifact. Group by authority; order numerically. No padding. »</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="str">
-        <v>NENA-STA-040.2-2024: §6.2, §6.2.1</v>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>NENA-STA-040.2-2024: §6.2, §6.2.1</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="str">
-        <v>NIST SP 800-53 Rev. 5: AC-2, AC-3, AC-5, AC-6</v>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5: AC-2, AC-3, AC-5, AC-6</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="str">
-        <v>Indiana statutes and administrative code: 240 IAC 5 (IDACS access)</v>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Indiana statutes and administrative code: 240 IAC 5 (IDACS access)</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="str">
-        <v>CJIS Security Policy v5.9: §5.5 (Access Control; CJIS-regulated access via IDACS)</v>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>CJIS Security Policy v5.9: §5.5 (Access Control; CJIS-regulated access via IDACS)</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="str">
-        <v>Revision History</v>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" t="str">
-        <v>Version</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Author</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Summary of Change</v>
-      </c>
-      <c r="E41"/>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Summary of Change</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n"/>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" t="str">
-        <v>{version}</v>
-      </c>
-      <c r="B42" t="str">
-        <v>{effectiveDate}</v>
-      </c>
-      <c r="C42" t="str">
-        <v>{reviewerRole}</v>
-      </c>
-      <c r="D42" t="str">
-        <v>{revisionNote}</v>
-      </c>
-      <c r="E42"/>
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>[#]</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>[Date]</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>[Role]</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>[Initial issue]</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="n"/>
     </row>
     <row r="44" ht="58" customHeight="1">
-      <c r="A44" t="str">
-        <v>Drafter's note (internal, delete before publishing): Re-typed from Inventory/Register to Reference Matrix. Built as a sparse list (one row per grant), not a dense grid, so it scales. Person-&gt;role lives in the Account-to-Role Assignment Register; reconciliation evidence in Privilege Review Records and Periodic Account Review.</v>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Drafter's note (internal, delete before publishing): Re-typed from Inventory/Register to Reference Matrix. Built as a sparse list (one row per grant), not a dense grid, so it scales. Person-&gt;role lives in the Account-to-Role Assignment Register; reconciliation evidence in Privilege Review Records and Periodic Account Review.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -539,152 +875,223 @@
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E44"/>
-  </ignoredErrors>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="24"/>
-    <col min="2" max="2" customWidth="1" width="50"/>
-    <col min="3" max="3" customWidth="1" width="14"/>
-    <col min="4" max="4" customWidth="1" width="32"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" t="str">
-        <v>Column Instructions &amp; How to Use</v>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Column Instructions &amp; How to Use</t>
+        </is>
       </c>
     </row>
     <row r="2" ht="43.5" customHeight="1">
-      <c r="A2" t="str">
-        <v>How to use this shell: this is the reusable Reference Matrix shell. Fill the header block on the Matrix tab, replace the corner / column / row headers with your dimensions, fill each cell, then delete every « » note before publishing.</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>How to use this shell: this is the reusable Reference Matrix shell. Fill the header block on the Matrix tab, replace the corner / column / row headers with your dimensions, fill each cell, then delete every « » note before publishing.</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="29.75" customHeight="1">
-      <c r="A3" t="str">
-        <v>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule and revision history live on the Matrix tab.</v>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule and revision history live on the Matrix tab.</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" t="str">
-        <v>How the matrix is structured</v>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>How the matrix is structured</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" t="str">
-        <v>Column</v>
-      </c>
-      <c r="B6" t="str">
-        <v>What it holds</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Required?</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Example value</v>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>What it holds</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Required?</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Example value</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" t="str">
-        <v>Corner cell</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Names the two dimensions: [row item] \ [attribute].</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Role \ System</v>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Corner cell</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Names the two dimensions: [row item] \ [attribute].</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Role \ System</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" t="str">
-        <v>Column headers</v>
-      </c>
-      <c r="B8" t="str">
-        <v>The attribute dimension across the top.</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D8" t="str">
-        <v>CAD, RMS, GIS, ALI</v>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Column headers</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>The attribute dimension across the top.</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>CAD, RMS, GIS, ALI</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" t="str">
-        <v>Row labels</v>
-      </c>
-      <c r="B9" t="str">
-        <v>The item dimension down the left (shaded).</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Dispatcher, Supervisor</v>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Row labels</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>The item dimension down the left (shaded).</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Dispatcher, Supervisor</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" t="str">
-        <v>Cells</v>
-      </c>
-      <c r="B10" t="str">
-        <v>The relationship value where a row meets a column.</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Read / Write / None</v>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Cells</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>The relationship value where a row meets a column.</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Read / Write / None</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" t="str">
-        <v>Profile Scaling Notes</v>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profile Scaling Notes</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" t="str">
-        <v>What minimum-viable upkeep looks like at each PSAP size. Keep all three rows while this ships as a template; once adopted, keep the one that fits.</v>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What minimum-viable upkeep looks like at each PSAP size. Keep all three rows while this ships as a template; once adopted, keep the one that fits.</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>PSAP Profile</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Minimum-viable implementation</v>
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSAP Profile</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minimum-viable implementation</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" t="str">
-        <v>Small (1–5, no in-house IT)</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Maintain this by hand. One person, usually the director, keeps it current on the review cycle in the header block.</v>
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small (1–5, no in-house IT)</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintain this by hand. One person, usually the director, keeps it current on the review cycle in the header block.</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" t="str">
-        <v>Medium (6–25, shared county IT)</v>
-      </c>
-      <c r="B16" t="str">
-        <v>A named coordinator owns it, updates it on a set cadence, and reconciles it at each periodic review.</v>
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium (6–25, shared county IT)</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A named coordinator owns it, updates it on a set cadence, and reconciles it at each periodic review.</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" t="str">
-        <v>Large (25+, dedicated IT/security)</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Where a system of record exists (asset, identity, badge, or finance system), populate it from there on a schedule and treat this sheet as the reviewed record.</v>
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large (25+, dedicated IT/security)</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where a system of record exists (asset, identity, badge, or finance system), populate it from there on a schedule and treat this sheet as the reviewed record.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -700,8 +1107,6 @@
     <mergeCell ref="B17:D17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
-  </ignoredErrors>
+  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/public/templates/forms/A-035-AccessEntitlementMatrix-FORM.xlsx
+++ b/public/templates/forms/A-035-AccessEntitlementMatrix-FORM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -526,7 +526,7 @@
     <row r="2" ht="29.75" customHeight="1">
       <c r="A2" s="8" t="n"/>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -614,7 +614,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="66.4" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Each row is one authorized grant: a role or vendor type paired with a system or data set and the access level allowed. The matrix is role-indexed; it states what each role may access, not who holds the role. The person-to-role assignment lives in the Account-to-Role Assignment Register, and reconciliation against live accounts is evidenced in the Privilege Review Records and Periodic Account Review / Certification Records.</t>
@@ -628,7 +628,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>« Replace the corner, column headers, and row labels with the dimensions this matrix maps (e.g., role × system, control × artifact). Add rows and columns as needed. »</t>
@@ -732,7 +732,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
+    <row r="30" ht="34.7" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Reviewed at least [quarterly] by the [role], and reconciled against active accounts each cycle. Update on any role or system change.</t>
@@ -874,8 +874,14 @@
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C18:C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Access level (read / write / adm" prompt="Select a value" type="list">
+      <formula1>"Read,Write,Admin"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -908,7 +914,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule and revision history live on the Matrix tab.</t>
@@ -1107,6 +1113,6 @@
     <mergeCell ref="B17:D17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>